--- a/RevenuePlan_Upload.xlsx
+++ b/RevenuePlan_Upload.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C3F0E47-4258-4A2E-9C3B-CD29A554016F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C2FEFE-01A8-4BD5-AEA6-293A8C75CA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1650" windowWidth="29040" windowHeight="15720" xr2:uid="{CC890FFC-E055-4E35-BB9B-45C996DBA1BC}"/>
+    <workbookView xWindow="43095" yWindow="1770" windowWidth="14610" windowHeight="15585" xr2:uid="{CC890FFC-E055-4E35-BB9B-45C996DBA1BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$116</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="82">
   <si>
     <t>Date</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -197,85 +200,105 @@
     <t>(주)현대홈쇼핑</t>
   </si>
   <si>
+    <t>11번가(위탁)</t>
+  </si>
+  <si>
+    <t>11번가</t>
+  </si>
+  <si>
+    <t>띵샵</t>
+  </si>
+  <si>
+    <t>롯데카드 주식회사</t>
+  </si>
+  <si>
+    <t>카카오</t>
+  </si>
+  <si>
+    <t>주식회사 카카오</t>
+  </si>
+  <si>
+    <t>GS홈쇼핑</t>
+  </si>
+  <si>
+    <t>자사몰</t>
+  </si>
+  <si>
+    <t>자사몰_스크럽대디</t>
+  </si>
+  <si>
+    <t>올리브영</t>
+  </si>
+  <si>
+    <t>29CM</t>
+  </si>
+  <si>
+    <t>(주)폼하이테크</t>
+  </si>
+  <si>
+    <t>코스트코</t>
+  </si>
+  <si>
+    <t>(주)코스트코코리아</t>
+  </si>
+  <si>
+    <t>(주)햅스토어</t>
+  </si>
+  <si>
+    <t>스크럽대디</t>
+  </si>
+  <si>
+    <t>도매(비정기)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>스크럽대디</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>㈜이마트</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>(주)호민상사</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>홈앤쇼핑</t>
   </si>
   <si>
     <t>(주)홈앤쇼핑</t>
   </si>
   <si>
-    <t>11번가(위탁)</t>
-  </si>
-  <si>
-    <t>11번가</t>
-  </si>
-  <si>
-    <t>띵샵</t>
-  </si>
-  <si>
-    <t>롯데카드 주식회사</t>
-  </si>
-  <si>
-    <t>카카오</t>
-  </si>
-  <si>
-    <t>주식회사 카카오</t>
-  </si>
-  <si>
     <t>온라인(비정기)</t>
   </si>
   <si>
-    <t>GS홈쇼핑</t>
-  </si>
-  <si>
     <t>(주)지에스리테일 홈쇼핑</t>
   </si>
   <si>
-    <t>자사몰</t>
-  </si>
-  <si>
-    <t>자사몰_스크럽대디</t>
-  </si>
-  <si>
-    <t>올리브영</t>
-  </si>
-  <si>
     <t>(주)씨제이올리브영</t>
   </si>
   <si>
-    <t>29CM</t>
-  </si>
-  <si>
     <t>(주)무신사</t>
   </si>
   <si>
-    <t>(주)폼하이테크</t>
-  </si>
-  <si>
-    <t>코스트코</t>
-  </si>
-  <si>
-    <t>(주)코스트코코리아</t>
-  </si>
-  <si>
-    <t>(주)햅스토어</t>
-  </si>
-  <si>
-    <t>㈜이마트</t>
-  </si>
-  <si>
-    <t>(주)호민상사</t>
-  </si>
-  <si>
-    <t>도매(비정기)</t>
+    <t>(주)우아한형제들</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>하나로모아산업(주)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>(주)이랜드리테일</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>(주)헬로우아폴로</t>
-  </si>
-  <si>
-    <t>스크럽대디</t>
-  </si>
-  <si>
-    <t>EXPECTED</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Expected</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -283,10 +306,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -316,6 +340,43 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="NanumGothicOTFLight"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -325,7 +386,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -333,8 +394,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -342,16 +429,62 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="쉼표 [0]" xfId="3" builtinId="6"/>
     <cellStyle name="쉼표 [0] 2" xfId="2" xr:uid="{C6192FC1-8AA1-4F25-A1E2-AA0037A6B5A9}"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 2" xfId="1" xr:uid="{4604BAFC-C9C2-4B03-9780-02B908B3F55E}"/>
@@ -686,7 +819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB91EFA-3FC0-48E9-8038-E1892C7DACF0}">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F116"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="11.08203125" bestFit="1" customWidth="1"/>
@@ -720,19 +853,19 @@
       <c r="A2" s="1">
         <v>46023</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F2">
+      <c r="D2" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" s="4">
         <v>133000000</v>
       </c>
     </row>
@@ -740,19 +873,19 @@
       <c r="A3" s="1">
         <v>46023</v>
       </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F3">
+      <c r="E3" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F3" s="5">
         <v>9000000</v>
       </c>
     </row>
@@ -760,19 +893,19 @@
       <c r="A4" s="1">
         <v>46023</v>
       </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E4" t="s">
-        <v>77</v>
-      </c>
-      <c r="F4">
+      <c r="E4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F4" s="5">
         <v>4604688</v>
       </c>
     </row>
@@ -780,19 +913,19 @@
       <c r="A5" s="1">
         <v>46023</v>
       </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F5">
+      <c r="E5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F5" s="5">
         <v>5000000</v>
       </c>
     </row>
@@ -800,19 +933,19 @@
       <c r="A6" s="1">
         <v>46023</v>
       </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B6" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E6" t="s">
-        <v>77</v>
-      </c>
-      <c r="F6">
+      <c r="E6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" s="6">
         <v>700000</v>
       </c>
     </row>
@@ -820,19 +953,19 @@
       <c r="A7" s="1">
         <v>46023</v>
       </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F7">
+      <c r="E7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="6">
         <v>6000000</v>
       </c>
     </row>
@@ -840,19 +973,19 @@
       <c r="A8" s="1">
         <v>46023</v>
       </c>
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B8" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E8" t="s">
-        <v>77</v>
-      </c>
-      <c r="F8">
+      <c r="E8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" s="6">
         <v>8100000</v>
       </c>
     </row>
@@ -860,19 +993,20 @@
       <c r="A9" s="1">
         <v>46023</v>
       </c>
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B9" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="E9" t="s">
-        <v>77</v>
-      </c>
-      <c r="F9">
+      <c r="E9" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" s="6">
+        <f>34000000-2100000-4000000</f>
         <v>27900000</v>
       </c>
     </row>
@@ -880,19 +1014,19 @@
       <c r="A10" s="1">
         <v>46023</v>
       </c>
-      <c r="B10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B10" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E10" t="s">
-        <v>77</v>
-      </c>
-      <c r="F10">
+      <c r="E10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" s="6">
         <v>15000000</v>
       </c>
     </row>
@@ -900,19 +1034,19 @@
       <c r="A11" s="1">
         <v>46023</v>
       </c>
-      <c r="B11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B11" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F11">
+      <c r="E11" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11" s="7">
         <v>2700000</v>
       </c>
     </row>
@@ -920,19 +1054,20 @@
       <c r="A12" s="1">
         <v>46023</v>
       </c>
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B12" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E12" t="s">
-        <v>77</v>
-      </c>
-      <c r="F12">
+      <c r="E12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" s="7">
+        <f>1900000+900000</f>
         <v>2800000</v>
       </c>
     </row>
@@ -940,19 +1075,19 @@
       <c r="A13" s="1">
         <v>46023</v>
       </c>
-      <c r="B13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B13" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F13">
+      <c r="E13" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" s="4">
         <v>1600000</v>
       </c>
     </row>
@@ -960,19 +1095,19 @@
       <c r="A14" s="1">
         <v>46023</v>
       </c>
-      <c r="B14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B14" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E14" t="s">
-        <v>77</v>
-      </c>
-      <c r="F14">
+      <c r="E14" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" s="4">
         <v>7895835</v>
       </c>
     </row>
@@ -980,19 +1115,19 @@
       <c r="A15" s="1">
         <v>46023</v>
       </c>
-      <c r="B15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B15" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D15" t="s">
-        <v>73</v>
-      </c>
-      <c r="E15" t="s">
-        <v>77</v>
-      </c>
-      <c r="F15">
+      <c r="D15" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" s="4">
         <v>5350000</v>
       </c>
     </row>
@@ -1000,19 +1135,19 @@
       <c r="A16" s="1">
         <v>46023</v>
       </c>
-      <c r="B16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="B16" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E16" t="s">
-        <v>77</v>
-      </c>
-      <c r="F16">
+      <c r="E16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="4">
         <v>3400000</v>
       </c>
     </row>
@@ -1020,19 +1155,19 @@
       <c r="A17" s="1">
         <v>46023</v>
       </c>
-      <c r="B17" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="B17" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E17" t="s">
-        <v>77</v>
-      </c>
-      <c r="F17">
+      <c r="E17" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="4">
         <v>150000</v>
       </c>
     </row>
@@ -1040,19 +1175,19 @@
       <c r="A18" s="1">
         <v>46023</v>
       </c>
-      <c r="B18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B18" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E18" t="s">
-        <v>77</v>
-      </c>
-      <c r="F18">
+      <c r="E18" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F18" s="4">
         <v>195000</v>
       </c>
     </row>
@@ -1060,19 +1195,19 @@
       <c r="A19" s="1">
         <v>46023</v>
       </c>
-      <c r="B19" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="B19" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E19" t="s">
-        <v>77</v>
-      </c>
-      <c r="F19">
+      <c r="E19" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F19" s="4">
         <v>1000000</v>
       </c>
     </row>
@@ -1080,19 +1215,19 @@
       <c r="A20" s="1">
         <v>46023</v>
       </c>
-      <c r="B20" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="B20" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E20" t="s">
-        <v>77</v>
-      </c>
-      <c r="F20">
+      <c r="E20" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F20" s="4">
         <v>1500000</v>
       </c>
     </row>
@@ -1100,19 +1235,19 @@
       <c r="A21" s="1">
         <v>46023</v>
       </c>
-      <c r="B21" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="B21" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E21" t="s">
-        <v>77</v>
-      </c>
-      <c r="F21">
+      <c r="E21" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" s="4">
         <v>900000</v>
       </c>
     </row>
@@ -1120,19 +1255,19 @@
       <c r="A22" s="1">
         <v>46023</v>
       </c>
-      <c r="B22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="B22" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E22" t="s">
-        <v>77</v>
-      </c>
-      <c r="F22">
+      <c r="E22" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F22" s="4">
         <v>500000</v>
       </c>
     </row>
@@ -1140,19 +1275,19 @@
       <c r="A23" s="1">
         <v>46023</v>
       </c>
-      <c r="B23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="B23" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="E23" t="s">
-        <v>77</v>
-      </c>
-      <c r="F23">
+      <c r="E23" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F23" s="4">
         <v>2300000</v>
       </c>
     </row>
@@ -1160,19 +1295,19 @@
       <c r="A24" s="1">
         <v>46023</v>
       </c>
-      <c r="B24" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="B24" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E24" t="s">
-        <v>77</v>
-      </c>
-      <c r="F24">
+      <c r="E24" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" s="4">
         <v>450000</v>
       </c>
     </row>
@@ -1180,19 +1315,19 @@
       <c r="A25" s="1">
         <v>46023</v>
       </c>
-      <c r="B25" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="B25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E25" t="s">
-        <v>77</v>
-      </c>
-      <c r="F25">
+      <c r="E25" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F25" s="4">
         <v>650000</v>
       </c>
     </row>
@@ -1200,19 +1335,20 @@
       <c r="A26" s="1">
         <v>46023</v>
       </c>
-      <c r="B26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" t="s">
-        <v>74</v>
-      </c>
-      <c r="D26" t="s">
-        <v>74</v>
-      </c>
-      <c r="E26" t="s">
-        <v>77</v>
-      </c>
-      <c r="F26">
+      <c r="B26" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" s="4">
+        <f>2800000+3500000</f>
         <v>6300000</v>
       </c>
     </row>
@@ -1220,19 +1356,19 @@
       <c r="A27" s="1">
         <v>46023</v>
       </c>
-      <c r="B27" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="B27" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="E27" t="s">
-        <v>77</v>
-      </c>
-      <c r="F27">
+      <c r="E27" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F27" s="8">
         <v>631000000</v>
       </c>
     </row>
@@ -1240,19 +1376,19 @@
       <c r="A28" s="1">
         <v>46023</v>
       </c>
-      <c r="B28" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="B28" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="E28" t="s">
-        <v>77</v>
-      </c>
-      <c r="F28">
+      <c r="E28" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F28" s="8">
         <v>10000000</v>
       </c>
     </row>
@@ -1260,19 +1396,19 @@
       <c r="A29" s="1">
         <v>46023</v>
       </c>
-      <c r="B29" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="B29" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E29" t="s">
-        <v>77</v>
-      </c>
-      <c r="F29">
+      <c r="E29" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29" s="8">
         <v>49322000</v>
       </c>
     </row>
@@ -1280,19 +1416,19 @@
       <c r="A30" s="1">
         <v>46023</v>
       </c>
-      <c r="B30" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="B30" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E30" t="s">
-        <v>77</v>
-      </c>
-      <c r="F30">
+      <c r="E30" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F30" s="8">
         <v>50000000</v>
       </c>
     </row>
@@ -1300,19 +1436,19 @@
       <c r="A31" s="1">
         <v>46023</v>
       </c>
-      <c r="B31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="B31" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E31" t="s">
-        <v>77</v>
-      </c>
-      <c r="F31">
+      <c r="E31" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F31" s="8">
         <v>2310000</v>
       </c>
     </row>
@@ -1320,19 +1456,19 @@
       <c r="A32" s="1">
         <v>46023</v>
       </c>
-      <c r="B32" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="B32" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E32" t="s">
-        <v>77</v>
-      </c>
-      <c r="F32">
+      <c r="E32" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F32" s="3">
         <v>154000</v>
       </c>
     </row>
@@ -1340,19 +1476,19 @@
       <c r="A33" s="1">
         <v>46023</v>
       </c>
-      <c r="B33" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="B33" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E33" t="s">
-        <v>77</v>
-      </c>
-      <c r="F33">
+      <c r="E33" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F33" s="3">
         <v>210000</v>
       </c>
     </row>
@@ -1360,19 +1496,19 @@
       <c r="A34" s="1">
         <v>46023</v>
       </c>
-      <c r="B34" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="B34" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E34" t="s">
-        <v>77</v>
-      </c>
-      <c r="F34">
+      <c r="E34" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F34" s="3">
         <v>5600000</v>
       </c>
     </row>
@@ -1380,19 +1516,19 @@
       <c r="A35" s="1">
         <v>46023</v>
       </c>
-      <c r="B35" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" t="s">
-        <v>51</v>
-      </c>
-      <c r="D35" t="s">
-        <v>52</v>
-      </c>
-      <c r="E35" t="s">
-        <v>77</v>
-      </c>
-      <c r="F35">
+      <c r="B35" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F35" s="3">
         <v>67000</v>
       </c>
     </row>
@@ -1400,19 +1536,19 @@
       <c r="A36" s="1">
         <v>46023</v>
       </c>
-      <c r="B36" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" t="s">
-        <v>53</v>
-      </c>
-      <c r="D36" t="s">
-        <v>54</v>
-      </c>
-      <c r="E36" t="s">
-        <v>77</v>
-      </c>
-      <c r="F36">
+      <c r="B36" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F36" s="3">
         <v>576000</v>
       </c>
     </row>
@@ -1420,19 +1556,19 @@
       <c r="A37" s="1">
         <v>46023</v>
       </c>
-      <c r="B37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" t="s">
-        <v>55</v>
-      </c>
-      <c r="D37" t="s">
-        <v>56</v>
-      </c>
-      <c r="E37" t="s">
-        <v>77</v>
-      </c>
-      <c r="F37">
+      <c r="B37" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F37" s="3">
         <v>365000</v>
       </c>
     </row>
@@ -1440,19 +1576,19 @@
       <c r="A38" s="1">
         <v>46023</v>
       </c>
-      <c r="B38" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" t="s">
-        <v>57</v>
-      </c>
-      <c r="D38" t="s">
-        <v>58</v>
-      </c>
-      <c r="E38" t="s">
-        <v>77</v>
-      </c>
-      <c r="F38">
+      <c r="B38" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F38" s="3">
         <v>78400</v>
       </c>
     </row>
@@ -1460,19 +1596,19 @@
       <c r="A39" s="1">
         <v>46023</v>
       </c>
-      <c r="B39" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" t="s">
-        <v>59</v>
-      </c>
-      <c r="D39" t="s">
-        <v>59</v>
-      </c>
-      <c r="E39" t="s">
-        <v>77</v>
-      </c>
-      <c r="F39">
+      <c r="B39" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F39" s="3">
         <v>140000</v>
       </c>
     </row>
@@ -1480,19 +1616,19 @@
       <c r="A40" s="1">
         <v>46023</v>
       </c>
-      <c r="B40" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" t="s">
-        <v>60</v>
-      </c>
-      <c r="D40" t="s">
-        <v>61</v>
-      </c>
-      <c r="E40" t="s">
-        <v>77</v>
-      </c>
-      <c r="F40">
+      <c r="B40" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F40" s="3">
         <v>1700000</v>
       </c>
     </row>
@@ -1500,19 +1636,19 @@
       <c r="A41" s="1">
         <v>46023</v>
       </c>
-      <c r="B41" t="s">
-        <v>76</v>
-      </c>
-      <c r="C41" t="s">
-        <v>62</v>
-      </c>
-      <c r="D41" t="s">
-        <v>63</v>
-      </c>
-      <c r="E41" t="s">
-        <v>77</v>
-      </c>
-      <c r="F41">
+      <c r="B41" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F41" s="3">
         <v>78587544.25</v>
       </c>
     </row>
@@ -1520,19 +1656,19 @@
       <c r="A42" s="1">
         <v>46023</v>
       </c>
-      <c r="B42" t="s">
-        <v>76</v>
-      </c>
-      <c r="C42" t="s">
-        <v>64</v>
-      </c>
-      <c r="D42" t="s">
-        <v>65</v>
-      </c>
-      <c r="E42" t="s">
-        <v>77</v>
-      </c>
-      <c r="F42">
+      <c r="B42" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F42" s="3">
         <v>16285057</v>
       </c>
     </row>
@@ -1540,19 +1676,19 @@
       <c r="A43" s="1">
         <v>46023</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D43" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="C43" t="s">
-        <v>66</v>
-      </c>
-      <c r="D43" t="s">
-        <v>67</v>
-      </c>
-      <c r="E43" t="s">
-        <v>77</v>
-      </c>
-      <c r="F43">
+      <c r="E43" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F43" s="3">
         <v>4931612</v>
       </c>
     </row>
@@ -1560,19 +1696,19 @@
       <c r="A44" s="1">
         <v>46023</v>
       </c>
-      <c r="B44" t="s">
-        <v>76</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="B44" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C44" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E44" t="s">
-        <v>77</v>
-      </c>
-      <c r="F44">
+      <c r="E44" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F44" s="3">
         <v>16040183.5</v>
       </c>
     </row>
@@ -1580,19 +1716,19 @@
       <c r="A45" s="1">
         <v>46023</v>
       </c>
-      <c r="B45" t="s">
-        <v>76</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="B45" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C45" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E45" t="s">
-        <v>77</v>
-      </c>
-      <c r="F45">
+      <c r="E45" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F45" s="3">
         <v>8126888</v>
       </c>
     </row>
@@ -1600,19 +1736,19 @@
       <c r="A46" s="1">
         <v>46023</v>
       </c>
-      <c r="B46" t="s">
-        <v>76</v>
-      </c>
-      <c r="C46" t="s">
+      <c r="B46" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C46" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E46" t="s">
-        <v>77</v>
-      </c>
-      <c r="F46">
+      <c r="E46" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F46" s="3">
         <v>4022369.4</v>
       </c>
     </row>
@@ -1620,19 +1756,19 @@
       <c r="A47" s="1">
         <v>46023</v>
       </c>
-      <c r="B47" t="s">
-        <v>76</v>
-      </c>
-      <c r="C47" t="s">
+      <c r="B47" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C47" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E47" t="s">
-        <v>77</v>
-      </c>
-      <c r="F47">
+      <c r="E47" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F47" s="3">
         <v>14455</v>
       </c>
     </row>
@@ -1640,19 +1776,19 @@
       <c r="A48" s="1">
         <v>46023</v>
       </c>
-      <c r="B48" t="s">
-        <v>76</v>
-      </c>
-      <c r="C48" t="s">
-        <v>68</v>
-      </c>
-      <c r="D48" t="s">
-        <v>68</v>
-      </c>
-      <c r="E48" t="s">
-        <v>77</v>
-      </c>
-      <c r="F48">
+      <c r="B48" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F48" s="3">
         <v>177297488</v>
       </c>
     </row>
@@ -1660,19 +1796,19 @@
       <c r="A49" s="1">
         <v>46023</v>
       </c>
-      <c r="B49" t="s">
-        <v>76</v>
-      </c>
-      <c r="C49" t="s">
-        <v>69</v>
-      </c>
-      <c r="D49" t="s">
-        <v>70</v>
-      </c>
-      <c r="E49" t="s">
-        <v>77</v>
-      </c>
-      <c r="F49">
+      <c r="B49" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F49" s="4">
         <v>227516800</v>
       </c>
     </row>
@@ -1680,19 +1816,19 @@
       <c r="A50" s="1">
         <v>46023</v>
       </c>
-      <c r="B50" t="s">
-        <v>76</v>
-      </c>
-      <c r="C50" t="s">
+      <c r="B50" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C50" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D50" t="s">
-        <v>72</v>
-      </c>
-      <c r="E50" t="s">
-        <v>77</v>
-      </c>
-      <c r="F50">
+      <c r="D50" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F50" s="5">
         <v>15000000</v>
       </c>
     </row>
@@ -1700,19 +1836,20 @@
       <c r="A51" s="1">
         <v>46023</v>
       </c>
-      <c r="B51" t="s">
-        <v>76</v>
-      </c>
-      <c r="C51" t="s">
+      <c r="B51" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C51" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E51" t="s">
-        <v>77</v>
-      </c>
-      <c r="F51">
+      <c r="E51" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F51" s="4">
+        <f>4*320*1*20740</f>
         <v>26547200</v>
       </c>
     </row>
@@ -1720,19 +1857,19 @@
       <c r="A52" s="1">
         <v>46023</v>
       </c>
-      <c r="B52" t="s">
-        <v>76</v>
-      </c>
-      <c r="C52" t="s">
+      <c r="B52" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C52" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E52" t="s">
-        <v>77</v>
-      </c>
-      <c r="F52">
+      <c r="E52" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F52" s="4">
         <v>2400000</v>
       </c>
     </row>
@@ -1740,19 +1877,19 @@
       <c r="A53" s="1">
         <v>46023</v>
       </c>
-      <c r="B53" t="s">
-        <v>76</v>
-      </c>
-      <c r="C53" t="s">
+      <c r="B53" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C53" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E53" t="s">
-        <v>77</v>
-      </c>
-      <c r="F53">
+      <c r="E53" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F53" s="6">
         <v>5800000</v>
       </c>
     </row>
@@ -1760,19 +1897,20 @@
       <c r="A54" s="1">
         <v>46023</v>
       </c>
-      <c r="B54" t="s">
-        <v>76</v>
-      </c>
-      <c r="C54" t="s">
+      <c r="B54" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C54" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E54" t="s">
-        <v>77</v>
-      </c>
-      <c r="F54">
+      <c r="E54" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F54" s="7">
+        <f>6800000+6000000</f>
         <v>12800000</v>
       </c>
     </row>
@@ -1780,19 +1918,19 @@
       <c r="A55" s="1">
         <v>46023</v>
       </c>
-      <c r="B55" t="s">
-        <v>76</v>
-      </c>
-      <c r="C55" t="s">
+      <c r="B55" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C55" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D55" t="s">
-        <v>17</v>
-      </c>
-      <c r="E55" t="s">
+      <c r="D55" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="F55">
+      <c r="E55" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F55" s="7">
         <v>3800000</v>
       </c>
     </row>
@@ -1800,19 +1938,19 @@
       <c r="A56" s="1">
         <v>46023</v>
       </c>
-      <c r="B56" t="s">
-        <v>76</v>
-      </c>
-      <c r="C56" t="s">
+      <c r="B56" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C56" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D56" t="s">
-        <v>18</v>
-      </c>
-      <c r="E56" t="s">
-        <v>77</v>
-      </c>
-      <c r="F56">
+      <c r="D56" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F56" s="7">
         <v>5000000</v>
       </c>
     </row>
@@ -1820,19 +1958,19 @@
       <c r="A57" s="1">
         <v>46023</v>
       </c>
-      <c r="B57" t="s">
-        <v>76</v>
-      </c>
-      <c r="C57" t="s">
+      <c r="B57" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C57" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D57" t="s">
-        <v>20</v>
-      </c>
-      <c r="E57" t="s">
-        <v>77</v>
-      </c>
-      <c r="F57">
+      <c r="D57" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F57" s="7">
         <v>800000</v>
       </c>
     </row>
@@ -1840,19 +1978,20 @@
       <c r="A58" s="1">
         <v>46023</v>
       </c>
-      <c r="B58" t="s">
-        <v>76</v>
-      </c>
-      <c r="C58" t="s">
+      <c r="B58" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C58" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E58" t="s">
-        <v>77</v>
-      </c>
-      <c r="F58">
+      <c r="E58" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F58" s="7">
+        <f>1500000+1200000</f>
         <v>2700000</v>
       </c>
     </row>
@@ -1860,19 +1999,19 @@
       <c r="A59" s="1">
         <v>46023</v>
       </c>
-      <c r="B59" t="s">
-        <v>76</v>
-      </c>
-      <c r="C59" t="s">
+      <c r="B59" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C59" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D59" t="s">
-        <v>71</v>
-      </c>
-      <c r="E59" t="s">
-        <v>77</v>
-      </c>
-      <c r="F59">
+      <c r="D59" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F59" s="4">
         <v>3000000</v>
       </c>
     </row>
@@ -1880,19 +2019,19 @@
       <c r="A60" s="1">
         <v>46023</v>
       </c>
-      <c r="B60" t="s">
-        <v>76</v>
-      </c>
-      <c r="C60" t="s">
+      <c r="B60" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C60" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D60" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E60" t="s">
-        <v>77</v>
-      </c>
-      <c r="F60">
+      <c r="E60" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F60" s="4">
         <v>2000000</v>
       </c>
     </row>
@@ -1900,19 +2039,19 @@
       <c r="A61" s="1">
         <v>46023</v>
       </c>
-      <c r="B61" t="s">
-        <v>76</v>
-      </c>
-      <c r="C61" t="s">
+      <c r="B61" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C61" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D61" t="s">
-        <v>75</v>
-      </c>
-      <c r="E61" t="s">
-        <v>77</v>
-      </c>
-      <c r="F61">
+      <c r="D61" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F61" s="4">
         <v>500000</v>
       </c>
     </row>
@@ -1920,21 +2059,453 @@
       <c r="A62" s="1">
         <v>46023</v>
       </c>
-      <c r="B62" t="s">
-        <v>76</v>
-      </c>
-      <c r="C62" t="s">
-        <v>74</v>
-      </c>
-      <c r="D62" t="s">
-        <v>74</v>
-      </c>
-      <c r="E62" t="s">
-        <v>77</v>
-      </c>
-      <c r="F62">
+      <c r="B62" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F62" s="4">
         <v>2800000</v>
       </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="1"/>
+      <c r="B63" s="10"/>
+      <c r="C63" s="10"/>
+      <c r="D63" s="9"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="6"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="1"/>
+      <c r="B64" s="10"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="6"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" s="1"/>
+      <c r="B65" s="11"/>
+      <c r="C65" s="11"/>
+      <c r="D65" s="9"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="6"/>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="1"/>
+      <c r="B66" s="11"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="6"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="1"/>
+      <c r="B67" s="11"/>
+      <c r="C67" s="11"/>
+      <c r="D67" s="9"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="7"/>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" s="1"/>
+      <c r="B68" s="11"/>
+      <c r="C68" s="11"/>
+      <c r="D68" s="9"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="7"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" s="1"/>
+      <c r="B69" s="10"/>
+      <c r="C69" s="10"/>
+      <c r="D69" s="9"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="4"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" s="1"/>
+      <c r="B70" s="10"/>
+      <c r="C70" s="10"/>
+      <c r="D70" s="9"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="4"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="1"/>
+      <c r="B71" s="10"/>
+      <c r="C71" s="10"/>
+      <c r="D71" s="13"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="4"/>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" s="1"/>
+      <c r="B72" s="10"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="13"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="4"/>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="1"/>
+      <c r="B73" s="10"/>
+      <c r="C73" s="10"/>
+      <c r="D73" s="9"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="4"/>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" s="1"/>
+      <c r="B74" s="10"/>
+      <c r="C74" s="10"/>
+      <c r="D74" s="9"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="4"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" s="1"/>
+      <c r="B75" s="10"/>
+      <c r="C75" s="10"/>
+      <c r="D75" s="9"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="4"/>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" s="1"/>
+      <c r="B76" s="10"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="9"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="4"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" s="1"/>
+      <c r="B77" s="10"/>
+      <c r="C77" s="10"/>
+      <c r="D77" s="9"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="4"/>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" s="1"/>
+      <c r="B78" s="11"/>
+      <c r="C78" s="11"/>
+      <c r="D78" s="9"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="4"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="1"/>
+      <c r="B79" s="11"/>
+      <c r="C79" s="11"/>
+      <c r="D79" s="9"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="4"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="1"/>
+      <c r="B80" s="11"/>
+      <c r="C80" s="11"/>
+      <c r="D80" s="9"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="4"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" s="1"/>
+      <c r="B81" s="11"/>
+      <c r="C81" s="11"/>
+      <c r="D81" s="9"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="4"/>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" s="1"/>
+      <c r="B82" s="11"/>
+      <c r="C82" s="11"/>
+      <c r="D82" s="10"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="4"/>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" s="1"/>
+      <c r="B83" s="11"/>
+      <c r="C83" s="11"/>
+      <c r="D83" s="9"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="8"/>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" s="1"/>
+      <c r="B84" s="11"/>
+      <c r="C84" s="11"/>
+      <c r="D84" s="9"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="8"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="1"/>
+      <c r="B85" s="11"/>
+      <c r="C85" s="11"/>
+      <c r="D85" s="9"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="8"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" s="1"/>
+      <c r="B86" s="11"/>
+      <c r="C86" s="11"/>
+      <c r="D86" s="9"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="8"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" s="1"/>
+      <c r="B87" s="11"/>
+      <c r="C87" s="11"/>
+      <c r="D87" s="9"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="8"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" s="1"/>
+      <c r="B88" s="6"/>
+      <c r="C88" s="10"/>
+      <c r="D88" s="9"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="3"/>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" s="1"/>
+      <c r="B89" s="6"/>
+      <c r="C89" s="9"/>
+      <c r="D89" s="9"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="3"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="1"/>
+      <c r="B90" s="6"/>
+      <c r="C90" s="10"/>
+      <c r="D90" s="9"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="3"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91" s="1"/>
+      <c r="B91" s="6"/>
+      <c r="C91" s="10"/>
+      <c r="D91" s="9"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="3"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" s="1"/>
+      <c r="B92" s="6"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="9"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="3"/>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" s="1"/>
+      <c r="B93" s="6"/>
+      <c r="C93" s="10"/>
+      <c r="D93" s="9"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="3"/>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" s="1"/>
+      <c r="B94" s="6"/>
+      <c r="C94" s="10"/>
+      <c r="D94" s="9"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="3"/>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" s="1"/>
+      <c r="B95" s="6"/>
+      <c r="C95" s="11"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="3"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="1"/>
+      <c r="B96" s="6"/>
+      <c r="C96" s="11"/>
+      <c r="D96" s="9"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="3"/>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" s="1"/>
+      <c r="B97" s="6"/>
+      <c r="C97" s="11"/>
+      <c r="D97" s="9"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="3"/>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" s="1"/>
+      <c r="B98" s="6"/>
+      <c r="C98" s="10"/>
+      <c r="D98" s="12"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="3"/>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" s="1"/>
+      <c r="B99" s="6"/>
+      <c r="C99" s="11"/>
+      <c r="D99" s="9"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="3"/>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" s="1"/>
+      <c r="B100" s="10"/>
+      <c r="C100" s="11"/>
+      <c r="D100" s="9"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="3"/>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" s="1"/>
+      <c r="B101" s="10"/>
+      <c r="C101" s="11"/>
+      <c r="D101" s="9"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="3"/>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" s="1"/>
+      <c r="B102" s="10"/>
+      <c r="C102" s="11"/>
+      <c r="D102" s="9"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="3"/>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103" s="1"/>
+      <c r="B103" s="10"/>
+      <c r="C103" s="10"/>
+      <c r="D103" s="9"/>
+      <c r="E103" s="2"/>
+      <c r="F103" s="3"/>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104" s="1"/>
+      <c r="B104" s="10"/>
+      <c r="C104" s="9"/>
+      <c r="D104" s="9"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="3"/>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" s="1"/>
+      <c r="B105" s="10"/>
+      <c r="C105" s="9"/>
+      <c r="D105" s="9"/>
+      <c r="E105" s="2"/>
+      <c r="F105" s="3"/>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" s="1"/>
+      <c r="B106" s="10"/>
+      <c r="C106" s="9"/>
+      <c r="D106" s="9"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="4"/>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" s="1"/>
+      <c r="B107" s="10"/>
+      <c r="C107" s="9"/>
+      <c r="D107" s="9"/>
+      <c r="E107" s="2"/>
+      <c r="F107" s="5"/>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" s="1"/>
+      <c r="B108" s="10"/>
+      <c r="C108" s="9"/>
+      <c r="D108" s="9"/>
+      <c r="E108" s="2"/>
+      <c r="F108" s="4"/>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" s="1"/>
+      <c r="B109" s="10"/>
+      <c r="C109" s="9"/>
+      <c r="D109" s="9"/>
+      <c r="E109" s="2"/>
+      <c r="F109" s="4"/>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" s="1"/>
+      <c r="B110" s="10"/>
+      <c r="C110" s="9"/>
+      <c r="D110" s="9"/>
+      <c r="E110" s="2"/>
+      <c r="F110" s="6"/>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111" s="1"/>
+      <c r="B111" s="10"/>
+      <c r="C111" s="9"/>
+      <c r="D111" s="9"/>
+      <c r="E111" s="2"/>
+      <c r="F111" s="7"/>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" s="1"/>
+      <c r="B112" s="10"/>
+      <c r="C112" s="9"/>
+      <c r="D112" s="9"/>
+      <c r="E112" s="2"/>
+      <c r="F112" s="7"/>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" s="1"/>
+      <c r="B113" s="10"/>
+      <c r="C113" s="9"/>
+      <c r="D113" s="9"/>
+      <c r="E113" s="2"/>
+      <c r="F113" s="7"/>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" s="1"/>
+      <c r="B114" s="10"/>
+      <c r="C114" s="12"/>
+      <c r="D114" s="9"/>
+      <c r="E114" s="2"/>
+      <c r="F114" s="7"/>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115" s="1"/>
+      <c r="B115" s="10"/>
+      <c r="C115" s="9"/>
+      <c r="D115" s="9"/>
+      <c r="E115" s="2"/>
+      <c r="F115" s="7"/>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116" s="1"/>
+      <c r="B116" s="14"/>
+      <c r="C116" s="9"/>
+      <c r="D116" s="9"/>
+      <c r="E116" s="2"/>
+      <c r="F116" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/RevenuePlan_Upload.xlsx
+++ b/RevenuePlan_Upload.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C2FEFE-01A8-4BD5-AEA6-293A8C75CA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05D11914-5FCB-4F1B-AEF8-9BCC4FB901AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="1770" windowWidth="14610" windowHeight="15585" xr2:uid="{CC890FFC-E055-4E35-BB9B-45C996DBA1BC}"/>
+    <workbookView xWindow="42045" yWindow="1770" windowWidth="14400" windowHeight="15585" xr2:uid="{CC890FFC-E055-4E35-BB9B-45C996DBA1BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="86">
   <si>
     <t>Date</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -116,9 +116,6 @@
     <t>서해현대유통</t>
   </si>
   <si>
-    <t>(주)꼬끼오</t>
-  </si>
-  <si>
     <t>국군복지단</t>
   </si>
   <si>
@@ -134,9 +131,6 @@
     <t>(주)리빙</t>
   </si>
   <si>
-    <t>(주)태산홀딩스</t>
-  </si>
-  <si>
     <t>(주)다인유통</t>
   </si>
   <si>
@@ -222,9 +216,6 @@
   </si>
   <si>
     <t>자사몰</t>
-  </si>
-  <si>
-    <t>자사몰_스크럽대디</t>
   </si>
   <si>
     <t>올리브영</t>
@@ -260,45 +251,69 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
+    <t>Expected</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로그</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>(주)호민상사</t>
+  </si>
+  <si>
+    <t>유레카이비즈</t>
+  </si>
+  <si>
+    <t>도매(비정기)</t>
+  </si>
+  <si>
+    <t>GS편의점</t>
+  </si>
+  <si>
+    <t>GS편의점/슈퍼</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>홈앤쇼핑</t>
-  </si>
-  <si>
-    <t>(주)홈앤쇼핑</t>
-  </si>
-  <si>
-    <t>온라인(비정기)</t>
-  </si>
-  <si>
-    <t>(주)지에스리테일 홈쇼핑</t>
-  </si>
-  <si>
-    <t>(주)씨제이올리브영</t>
-  </si>
-  <si>
-    <t>(주)무신사</t>
-  </si>
-  <si>
-    <t>(주)우아한형제들</t>
+    <t>(주)헬로우아폴로</t>
+  </si>
+  <si>
+    <t>롯데쇼핑</t>
+  </si>
+  <si>
+    <t>롯데쇼핑(주)</t>
+  </si>
+  <si>
+    <t>자사몰_프로그</t>
+  </si>
+  <si>
+    <t>GS홈쇼핑 (신규)</t>
+  </si>
+  <si>
+    <t>자사몰</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>하나로모아산업(주)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>(주)이랜드리테일</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>(주)헬로우아폴로</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Expected</t>
+    <t>카카오선물하기</t>
+  </si>
+  <si>
+    <t>롯데마트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자사몰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>29CM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘의집</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>올리브영</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -310,7 +325,7 @@
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -377,6 +392,14 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -433,7 +456,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -480,6 +503,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -819,12 +845,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB91EFA-3FC0-48E9-8038-E1892C7DACF0}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:F116"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="11.08203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.58203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.25" customWidth="1"/>
     <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
@@ -849,9 +877,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" hidden="1">
       <c r="A2" s="1">
-        <v>46023</v>
+        <v>46113</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>6</v>
@@ -860,1220 +888,1178 @@
         <v>7</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F2" s="4">
-        <v>133000000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>147500000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" hidden="1">
       <c r="A3" s="1">
-        <v>46023</v>
+        <v>46113</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F3" s="5">
         <v>9000000</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" hidden="1">
       <c r="A4" s="1">
-        <v>46023</v>
+        <v>46113</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>9</v>
+      <c r="C4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F4" s="5">
-        <v>4604688</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>4000000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" hidden="1">
       <c r="A5" s="1">
-        <v>46023</v>
+        <v>46113</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>10</v>
+      <c r="C5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>11</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F5" s="5">
-        <v>5000000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>67</v>
+      </c>
+      <c r="F5" s="6">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" hidden="1">
       <c r="A6" s="1">
-        <v>46023</v>
+        <v>46113</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>11</v>
+      <c r="C6" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F6" s="6">
-        <v>700000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" hidden="1">
       <c r="A7" s="1">
-        <v>46023</v>
+        <v>46113</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>81</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F7" s="6">
-        <v>6000000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>14200000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" hidden="1">
       <c r="A8" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B8" s="10" t="s">
+        <v>46113</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>14</v>
+      <c r="C8" s="11" t="s">
+        <v>16</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F8" s="6">
-        <v>8100000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>39500000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" hidden="1">
       <c r="A9" s="1">
-        <v>46023</v>
+        <v>46113</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>17</v>
+      <c r="C9" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F9" s="6">
-        <f>34000000-2100000-4000000</f>
-        <v>27900000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>15000000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" hidden="1">
       <c r="A10" s="1">
-        <v>46023</v>
+        <v>46113</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>18</v>
+      <c r="C10" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>20</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F10" s="6">
-        <v>15000000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>67</v>
+      </c>
+      <c r="F10" s="7">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" hidden="1">
       <c r="A11" s="1">
-        <v>46023</v>
+        <v>46113</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>20</v>
+      <c r="C11" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>22</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F11" s="7">
-        <v>2700000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>4005600</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" hidden="1">
       <c r="A12" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B12" s="11" t="s">
+        <v>46113</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>22</v>
+      <c r="C12" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>23</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F12" s="7">
-        <f>1900000+900000</f>
-        <v>2800000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>67</v>
+      </c>
+      <c r="F12" s="4">
+        <v>5345443</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" hidden="1">
       <c r="A13" s="1">
-        <v>46023</v>
+        <v>46113</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>23</v>
+      <c r="C13" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F13" s="4">
-        <v>1600000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>8100000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" hidden="1">
       <c r="A14" s="1">
-        <v>46023</v>
+        <v>46113</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>24</v>
+      <c r="C14" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>70</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F14" s="4">
-        <v>7895835</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>5422350</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" hidden="1">
       <c r="A15" s="1">
-        <v>46023</v>
+        <v>46113</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="10" t="s">
-        <v>70</v>
+      <c r="D15" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F15" s="4">
-        <v>5350000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>3400000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" hidden="1">
       <c r="A16" s="1">
-        <v>46023</v>
+        <v>46113</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="10" t="s">
+      <c r="C16" s="10" t="s">
         <v>25</v>
       </c>
+      <c r="D16" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="E16" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F16" s="4">
-        <v>3400000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" hidden="1">
       <c r="A17" s="1">
-        <v>46023</v>
+        <v>46113</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="9" t="s">
         <v>26</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F17" s="4">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" hidden="1">
       <c r="A18" s="1">
-        <v>46023</v>
+        <v>46113</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="10" t="s">
-        <v>27</v>
-      </c>
       <c r="E18" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F18" s="4">
-        <v>195000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>1900000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" hidden="1">
       <c r="A19" s="1">
-        <v>46023</v>
+        <v>46113</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F19" s="4">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" hidden="1">
       <c r="A20" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B20" s="10" t="s">
+        <v>46113</v>
+      </c>
+      <c r="B20" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="9" t="s">
         <v>29</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F20" s="4">
-        <v>1500000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" hidden="1">
       <c r="A21" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B21" s="10" t="s">
+        <v>46113</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="9" t="s">
         <v>30</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F21" s="4">
-        <v>900000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" hidden="1">
       <c r="A22" s="1">
-        <v>46023</v>
+        <v>46113</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="9" t="s">
         <v>31</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F22" s="4">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" hidden="1">
       <c r="A23" s="1">
-        <v>46023</v>
+        <v>46113</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="10" t="s">
         <v>32</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F23" s="4">
-        <v>2300000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>650000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" hidden="1">
       <c r="A24" s="1">
-        <v>46023</v>
+        <v>46113</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="8">
+        <v>16000000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" hidden="1">
+      <c r="A25" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25" s="8">
+        <v>290000000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" hidden="1">
+      <c r="A26" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F26" s="8">
+        <v>35000000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" hidden="1">
+      <c r="A27" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F27" s="8">
+        <v>41811840</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" hidden="1">
+      <c r="A28" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F28" s="8">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" hidden="1">
+      <c r="A29" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F29" s="3">
+        <v>4000000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" hidden="1">
+      <c r="A30" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F30" s="3">
+        <v>4000000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" hidden="1">
+      <c r="A31" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F31" s="3">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" hidden="1">
+      <c r="A32" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F32" s="3">
+        <v>7500000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" hidden="1">
+      <c r="A33" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F33" s="3">
+        <v>20000000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" hidden="1">
+      <c r="A34" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F34" s="3">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" hidden="1">
+      <c r="A35" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C35" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D35" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F35" s="3">
+        <v>1800000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" hidden="1">
+      <c r="A36" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F36" s="3">
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" hidden="1">
+      <c r="A37" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F37" s="3">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" hidden="1">
+      <c r="A38" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F38" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" hidden="1">
+      <c r="A39" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F39" s="3">
+        <v>7300000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" hidden="1">
+      <c r="A40" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F40" s="3">
+        <v>3114800</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" hidden="1">
+      <c r="A41" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F24" s="4">
-        <v>450000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D25" s="11" t="s">
+      <c r="D41" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F25" s="4">
-        <v>650000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F26" s="4">
-        <f>2800000+3500000</f>
-        <v>6300000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="9" t="s">
+      <c r="E41" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F41" s="3">
+        <v>544240000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" hidden="1">
+      <c r="A42" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C42" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D42" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F27" s="8">
-        <v>631000000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="9" t="s">
+      <c r="E42" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F42" s="3">
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" hidden="1">
+      <c r="A43" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F43" s="3">
+        <v>61500000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" hidden="1">
+      <c r="A44" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D44" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F28" s="8">
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F29" s="8">
-        <v>49322000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="9" t="s">
+      <c r="E44" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F44" s="3">
+        <v>83080000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" hidden="1">
+      <c r="A45" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F45" s="4">
+        <v>8500000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" hidden="1">
+      <c r="A46" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D46" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F30" s="8">
-        <v>50000000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="9" t="s">
+      <c r="E46" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F46" s="5">
+        <v>1700000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" hidden="1">
+      <c r="A47" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F47" s="4">
+        <v>4350000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" hidden="1">
+      <c r="A48" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F48" s="4">
+        <v>440000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" hidden="1">
+      <c r="A49" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F49" s="7">
+        <v>85000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" hidden="1">
+      <c r="A50" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F50" s="7">
+        <v>186800</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" hidden="1">
+      <c r="A51" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F51" s="7">
+        <v>48300000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" hidden="1">
+      <c r="A52" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F52" s="7">
+        <v>1700000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" hidden="1">
+      <c r="A53" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C53" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D53" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F31" s="8">
-        <v>2310000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F32" s="3">
-        <v>154000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F33" s="3">
-        <v>210000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F34" s="3">
-        <v>5600000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F35" s="3">
-        <v>67000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F36" s="3">
-        <v>576000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F37" s="3">
-        <v>365000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F38" s="3">
-        <v>78400</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F39" s="3">
-        <v>140000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F40" s="3">
-        <v>1700000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F41" s="3">
-        <v>78587544.25</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F42" s="3">
-        <v>16285057</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D43" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F43" s="3">
-        <v>4931612</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B44" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D44" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F44" s="3">
-        <v>16040183.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D45" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F45" s="3">
-        <v>8126888</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D46" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F46" s="3">
-        <v>4022369.4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B47" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D47" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F47" s="3">
-        <v>14455</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D48" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F48" s="3">
-        <v>177297488</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B49" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C49" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D49" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F49" s="4">
-        <v>227516800</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F50" s="5">
-        <v>15000000</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F51" s="4">
-        <f>4*320*1*20740</f>
-        <v>26547200</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F52" s="4">
-        <v>2400000</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B53" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>13</v>
-      </c>
       <c r="E53" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F53" s="6">
-        <v>5800000</v>
+        <v>67</v>
+      </c>
+      <c r="F53" s="7">
+        <v>92000</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C54" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>15</v>
+        <v>46113</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>79</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F54" s="7">
-        <f>6800000+6000000</f>
-        <v>12800000</v>
+        <v>117785396.31999999</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>16</v>
+        <v>46113</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>83</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F55" s="7">
-        <v>3800000</v>
+        <v>4905063.75</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B56" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C56" s="9" t="s">
-        <v>18</v>
+        <v>46113</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>84</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F56" s="7">
-        <v>5000000</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
+        <v>3262833.84</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" hidden="1">
       <c r="A57" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C57" s="9" t="s">
-        <v>19</v>
+        <v>46113</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>53</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F57" s="7">
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
+        <v>3340909</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" hidden="1">
       <c r="A58" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B58" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>21</v>
+        <v>46113</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F58" s="7">
-        <f>1500000+1200000</f>
-        <v>2700000</v>
+        <v>218223921</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B59" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>21</v>
+        <v>46113</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F59" s="4">
-        <v>3000000</v>
+        <v>67</v>
+      </c>
+      <c r="F59" s="7">
+        <v>9376651</v>
       </c>
     </row>
     <row r="60" spans="1:6">
-      <c r="A60" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B60" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D60" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F60" s="4">
-        <v>2000000</v>
-      </c>
+      <c r="A60" s="1"/>
+      <c r="B60" s="15"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="10"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="4"/>
     </row>
     <row r="61" spans="1:6">
-      <c r="A61" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B61" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C61" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D61" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F61" s="4">
-        <v>500000</v>
-      </c>
+      <c r="A61" s="1"/>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="4"/>
     </row>
     <row r="62" spans="1:6">
-      <c r="A62" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B62" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C62" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D62" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F62" s="4">
-        <v>2800000</v>
-      </c>
+      <c r="A62" s="1"/>
+      <c r="B62" s="9"/>
+      <c r="C62" s="10"/>
+      <c r="D62" s="10"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="4"/>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="1"/>
@@ -2508,6 +2494,16 @@
       <c r="F116" s="4"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F59" xr:uid="{4EB91EFA-3FC0-48E9-8038-E1892C7DACF0}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="(주)무신사"/>
+        <filter val="(주)버킷플레이스"/>
+        <filter val="(주)씨제이올리브영"/>
+        <filter val="자사몰_프로그"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
